--- a/backend/data/04_COMERCIAL.xlsx
+++ b/backend/data/04_COMERCIAL.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="86">
   <si>
     <t>ID_LEAD</t>
   </si>
@@ -128,6 +128,12 @@
   </si>
   <si>
     <t>PRO_000005</t>
+  </si>
+  <si>
+    <t>PRO_000006</t>
+  </si>
+  <si>
+    <t>PRO_000007</t>
   </si>
   <si>
     <t>ID_ITEM_PROPOSTA</t>
@@ -692,7 +698,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -700,10 +706,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -714,7 +720,7 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -725,7 +731,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -733,10 +739,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -744,10 +750,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -755,10 +761,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -766,10 +772,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -863,7 +869,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -978,6 +984,34 @@
         <v>46278</v>
       </c>
       <c r="D6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46278</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46278</v>
+      </c>
+      <c r="D8" t="s">
         <v>31</v>
       </c>
     </row>
@@ -994,16 +1028,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -1022,7 +1056,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
@@ -1031,10 +1065,10 @@
         <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>24</v>
@@ -1053,13 +1087,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>24</v>
@@ -1078,16 +1112,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1103,48 +1137,48 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
@@ -1185,7 +1219,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
@@ -1226,7 +1260,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
         <v>33</v>
@@ -1267,7 +1301,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
@@ -1308,7 +1342,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -1349,7 +1383,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
@@ -1390,7 +1424,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -1431,7 +1465,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
@@ -1472,7 +1506,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
@@ -1513,7 +1547,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
@@ -1554,7 +1588,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
@@ -1595,7 +1629,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -1636,7 +1670,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>

--- a/backend/data/04_COMERCIAL.xlsx
+++ b/backend/data/04_COMERCIAL.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
   <si>
     <t>ID_LEAD</t>
   </si>
@@ -88,6 +88,18 @@
     <t>EQP_000003</t>
   </si>
   <si>
+    <t>NEG_000003</t>
+  </si>
+  <si>
+    <t>ALU_000003</t>
+  </si>
+  <si>
+    <t>SER_000013</t>
+  </si>
+  <si>
+    <t>EQP_000002</t>
+  </si>
+  <si>
     <t>ID_PROPOSTA</t>
   </si>
   <si>
@@ -134,6 +146,9 @@
   </si>
   <si>
     <t>PRO_000007</t>
+  </si>
+  <si>
+    <t>PRO_000008</t>
   </si>
   <si>
     <t>ID_ITEM_PROPOSTA</t>
@@ -698,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -706,10 +721,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -720,7 +735,7 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -731,7 +746,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -739,10 +754,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -750,10 +765,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -761,10 +776,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -772,10 +787,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -789,7 +804,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -859,6 +874,29 @@
       </c>
       <c r="G3" s="2">
         <v>46273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46279</v>
       </c>
     </row>
   </sheetData>
@@ -869,45 +907,45 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -916,12 +954,12 @@
         <v>46272</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -930,12 +968,12 @@
         <v>46272</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -944,7 +982,7 @@
         <v>46272</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E4">
         <v>1971.9</v>
@@ -961,7 +999,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -970,12 +1008,12 @@
         <v>46272</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -984,12 +1022,12 @@
         <v>46278</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -998,12 +1036,12 @@
         <v>46278</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1012,7 +1050,21 @@
         <v>46278</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46278</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1028,19 +1080,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1056,22 +1108,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1087,16 +1139,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1112,16 +1164,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1137,51 +1189,51 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1219,10 +1271,10 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1260,10 +1312,10 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1301,10 +1353,10 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1342,10 +1394,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1383,10 +1435,10 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1424,10 +1476,10 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1465,10 +1517,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1506,10 +1558,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1547,10 +1599,10 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1588,10 +1640,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1629,10 +1681,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1670,10 +1722,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>13</v>

--- a/backend/data/04_COMERCIAL.xlsx
+++ b/backend/data/04_COMERCIAL.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="95">
   <si>
     <t>ID_LEAD</t>
   </si>
@@ -100,6 +100,15 @@
     <t>EQP_000002</t>
   </si>
   <si>
+    <t>NEG_000004</t>
+  </si>
+  <si>
+    <t>ALU_000004</t>
+  </si>
+  <si>
+    <t>SER_000018</t>
+  </si>
+  <si>
     <t>ID_PROPOSTA</t>
   </si>
   <si>
@@ -149,6 +158,9 @@
   </si>
   <si>
     <t>PRO_000008</t>
+  </si>
+  <si>
+    <t>PRO_000009</t>
   </si>
   <si>
     <t>ID_ITEM_PROPOSTA</t>
@@ -713,7 +725,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -721,10 +733,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -735,7 +747,7 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -746,7 +758,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -754,10 +766,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -765,10 +777,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -776,10 +788,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -787,10 +799,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -804,7 +816,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -897,6 +909,29 @@
       </c>
       <c r="G4" s="2">
         <v>46279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46280</v>
       </c>
     </row>
   </sheetData>
@@ -907,45 +942,45 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -954,12 +989,12 @@
         <v>46272</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -968,12 +1003,12 @@
         <v>46272</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -982,7 +1017,7 @@
         <v>46272</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>1971.9</v>
@@ -999,7 +1034,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -1008,12 +1043,12 @@
         <v>46272</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -1022,12 +1057,12 @@
         <v>46278</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -1036,12 +1071,12 @@
         <v>46278</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1050,12 +1085,12 @@
         <v>46278</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -1064,7 +1099,21 @@
         <v>46278</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46280</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1080,19 +1129,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1108,22 +1157,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1139,16 +1188,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1164,16 +1213,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1189,51 +1238,51 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1271,10 +1320,10 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1312,10 +1361,10 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1353,10 +1402,10 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1394,10 +1443,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1435,10 +1484,10 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1476,10 +1525,10 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -1517,10 +1566,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1558,10 +1607,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1599,10 +1648,10 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1640,10 +1689,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -1681,10 +1730,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -1722,10 +1771,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C14">
         <v>13</v>
